--- a/Resultados080526.xlsx
+++ b/Resultados080526.xlsx
@@ -424,15 +424,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -907,8 +904,8 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -923,8 +920,8 @@
       <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -939,10 +936,10 @@
       <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -957,8 +954,8 @@
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -973,8 +970,8 @@
       <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -989,8 +986,8 @@
       <c r="D7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -1005,10 +1002,10 @@
       <c r="D8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -1023,8 +1020,8 @@
       <c r="D9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1041,8 +1038,8 @@
       <c r="D10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1059,8 +1056,8 @@
       <c r="D11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
@@ -1075,8 +1072,8 @@
       <c r="D12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1093,10 +1090,10 @@
       <c r="D13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
@@ -1111,10 +1108,10 @@
       <c r="D14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
@@ -1129,8 +1126,8 @@
       <c r="D15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
@@ -1145,8 +1142,8 @@
       <c r="D16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
@@ -1161,8 +1158,8 @@
       <c r="D17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
@@ -1177,8 +1174,8 @@
       <c r="D18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
+      <c r="E18" s="2"/>
+      <c r="F18" s="2" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1195,8 +1192,8 @@
       <c r="D19" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
@@ -1211,8 +1208,8 @@
       <c r="D20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="4" t="s">
+      <c r="E20" s="2"/>
+      <c r="F20" s="3" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1229,8 +1226,8 @@
       <c r="D21" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
@@ -1245,8 +1242,8 @@
       <c r="D22" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
@@ -1261,8 +1258,8 @@
       <c r="D23" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
@@ -1277,10 +1274,10 @@
       <c r="D24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
@@ -1295,10 +1292,10 @@
       <c r="D25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
@@ -1313,7 +1310,7 @@
       <c r="D26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E26" s="3"/>
+      <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
         <v>75</v>
       </c>
@@ -1331,8 +1328,8 @@
       <c r="D27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
@@ -1347,8 +1344,8 @@
       <c r="D28" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
@@ -1363,8 +1360,8 @@
       <c r="D29" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
@@ -1379,8 +1376,8 @@
       <c r="D30" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
@@ -1395,8 +1392,8 @@
       <c r="D31" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
@@ -1411,7 +1408,7 @@
       <c r="D32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E32" s="3"/>
+      <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
         <v>75</v>
       </c>
@@ -1429,8 +1426,8 @@
       <c r="D33" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Resultados080526.xlsx
+++ b/Resultados080526.xlsx
@@ -523,6 +523,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Resultados080526.xlsx
+++ b/Resultados080526.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="80" documentId="8_{DFA57357-67B5-45DD-BE1B-46E48544B083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{742B2BD8-295C-4063-AAC9-99FF80D2676B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF43666F-7D74-41D8-A8EC-929DF723E928}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{BF43666F-7D74-41D8-A8EC-929DF723E928}"/>
   </bookViews>
   <sheets>
     <sheet name="Notas080526_OrganizacionSubgere" sheetId="2" r:id="rId1"/>

--- a/Resultados080526.xlsx
+++ b/Resultados080526.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ingeurbe-my.sharepoint.com/personal/cpulgarin_construccion_com_co/Documents/1. Proyectos/1.4. Tour IA/1.4.5. Presentacion resultados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{DFA57357-67B5-45DD-BE1B-46E48544B083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{742B2BD8-295C-4063-AAC9-99FF80D2676B}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{DFA57357-67B5-45DD-BE1B-46E48544B083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5636F922-676E-4E7F-A0BD-BC5D78F85E0D}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{BF43666F-7D74-41D8-A8EC-929DF723E928}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF43666F-7D74-41D8-A8EC-929DF723E928}"/>
   </bookViews>
   <sheets>
     <sheet name="Notas080526_OrganizacionSubgere" sheetId="2" r:id="rId1"/>
@@ -61,9 +61,6 @@
     <t>proyecto</t>
   </si>
   <si>
-    <t>tecnologia</t>
-  </si>
-  <si>
     <t>0GqL19P0XepjiOoeFtsd</t>
   </si>
   <si>
@@ -359,6 +356,9 @@
   </si>
   <si>
     <t>Amarrado a SRM</t>
+  </si>
+  <si>
+    <t>DOLIENTE</t>
   </si>
 </sst>
 </file>
@@ -559,7 +559,7 @@
     <tableColumn id="1" xr3:uid="{CE5EA56F-CAC8-41C3-92A2-25B269DA51CE}" uniqueName="1" name="Document ID" queryTableFieldId="1" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{FDD0A4A8-FB75-41CE-A78A-7DEB9F99DA39}" uniqueName="2" name="contenido" queryTableFieldId="2" dataDxfId="4"/>
     <tableColumn id="6" xr3:uid="{49A1F630-7E34-4E5F-9433-839580678B05}" uniqueName="6" name="proyecto" queryTableFieldId="6" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{C4CB7353-0F7D-425F-BDBF-998487A13EB1}" uniqueName="7" name="tecnologia" queryTableFieldId="7" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{C4CB7353-0F7D-425F-BDBF-998487A13EB1}" uniqueName="7" name="DOLIENTE" queryTableFieldId="7" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{542D3633-E823-4ED1-9E2E-B5F082F776E4}" uniqueName="3" name="Estado" queryTableFieldId="11" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{EC1EAE08-5EAA-4DC8-8E36-B57604BB3E29}" uniqueName="4" name="Observacion" queryTableFieldId="12" dataDxfId="0"/>
   </tableColumns>
@@ -886,549 +886,549 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>

--- a/Resultados080526.xlsx
+++ b/Resultados080526.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ingeurbe-my.sharepoint.com/personal/cpulgarin_construccion_com_co/Documents/1. Proyectos/1.4. Tour IA/1.4.5. Presentacion resultados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{DFA57357-67B5-45DD-BE1B-46E48544B083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5636F922-676E-4E7F-A0BD-BC5D78F85E0D}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{DFA57357-67B5-45DD-BE1B-46E48544B083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30BC71A0-8D68-4374-85FF-8438C8D08816}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF43666F-7D74-41D8-A8EC-929DF723E928}"/>
   </bookViews>
   <sheets>
     <sheet name="Notas080526_OrganizacionSubgere" sheetId="2" r:id="rId1"/>
+    <sheet name="Por Frecuencia" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="DatosExternos_1" localSheetId="0" hidden="1">Notas080526_OrganizacionSubgere!$A$1:$D$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Frecuencia'!$A$1:$J$45</definedName>
+    <definedName name="DatosExternos_1" localSheetId="0" hidden="1">Notas080526_OrganizacionSubgere!$A$1:$E$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="171">
   <si>
     <t>Document ID</t>
   </si>
@@ -359,13 +361,217 @@
   </si>
   <si>
     <t>DOLIENTE</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Nombre Ineficiencia</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Reserva del Lago (RL)</t>
+  </si>
+  <si>
+    <t>Viale (VI)</t>
+  </si>
+  <si>
+    <t>Madero (MA)</t>
+  </si>
+  <si>
+    <t>Américas (AM)</t>
+  </si>
+  <si>
+    <t>Consulta Peregrino</t>
+  </si>
+  <si>
+    <t>Sesiones</t>
+  </si>
+  <si>
+    <t>SINCO</t>
+  </si>
+  <si>
+    <t>Portero, ARHI, Bitácora y Temporal no articulados · proceso manual · sin bloqueo por condición médica</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>Pedidos en Excel antes de SINCO — doble digitación sin valor</t>
+  </si>
+  <si>
+    <t>Aprobación en Excel y re-digitación en SINCO · SSTA sin acceso · proyección manual</t>
+  </si>
+  <si>
+    <t>Correos distintos por obra · proveedor no sabe a cuál enviar · OC no llega al proveedor</t>
+  </si>
+  <si>
+    <t>Base de presupuesto SINCO se recarga manualmente cada vez</t>
+  </si>
+  <si>
+    <t>Cuadro comparativo sin actualización automática · memorias no estandarizadas · control frena 3 meses antes</t>
+  </si>
+  <si>
+    <t>Cobro tarde · equipos en desuso sin alerta · control en manos de residentes · sin preacta automática</t>
+  </si>
+  <si>
+    <t>Cada obra con su cuadro · laboratorios no comparten bases · sin comparación automática con norma</t>
+  </si>
+  <si>
+    <t>Pago depende de Excel · causación y pago desarticulados · tesorería sin programación automática</t>
+  </si>
+  <si>
+    <t>Preactas digitales y soportes — estándar de memorias y firma digital</t>
+  </si>
+  <si>
+    <t>Preacta en SINCO sin estandarizar · memorias sin formato único · firma digital pendiente</t>
+  </si>
+  <si>
+    <t>Control de equipos: sin inventario — informe no genera preacta</t>
+  </si>
+  <si>
+    <t>No se sabe qué hay en obra · preacta manual · módulo Portero sin aprovechar</t>
+  </si>
+  <si>
+    <t>Sin incentivos · sin conexión BIM · módulo de calidad SINCO sin explotar</t>
+  </si>
+  <si>
+    <t>Salidas de almacén: flujo excesivo · prueba piloto parada</t>
+  </si>
+  <si>
+    <t>Vale físico · múltiples aprobaciones · maestros sin visibilidad de inventario</t>
+  </si>
+  <si>
+    <t>Creación de contratistas: hasta un mes, duplicada entre sociedades</t>
+  </si>
+  <si>
+    <t>Mismos contratistas aprobados por separado en cada sociedad · SRM en proceso</t>
+  </si>
+  <si>
+    <t>Tipologia de contratistas - tipo de contrato por actividad económica</t>
+  </si>
+  <si>
+    <t>Obra asigna tipo cuando debería ser contabilidad · error se detecta con la factura · 120 opciones reteICA</t>
+  </si>
+  <si>
+    <t>Relación de pagos enviada por Excel a tesorería</t>
+  </si>
+  <si>
+    <t>Obra hace la relación manualmente · contabilidad debe validar antes · no integrado en SINCO</t>
+  </si>
+  <si>
+    <t>Sin cruce de número de contrato con pago · cuadro Excel manual · sin validación legal automatizada</t>
+  </si>
+  <si>
+    <t>Vencimiento de contratos y pólizas sin alertas anticipadas</t>
+  </si>
+  <si>
+    <t>Se enteran al generar el corte · Ing. Forero aprueba solo viernes · alerta debe ser 3 semanas antes</t>
+  </si>
+  <si>
+    <t>Remisión del proveedor debe subirse digital a SINCO · debe traer número de OC · sin impresión de entrada</t>
+  </si>
+  <si>
+    <t>Minutas SINCO: datos repetitivos, pipeline sin parametrizar por monto</t>
+  </si>
+  <si>
+    <t>Subgerente, cédulas, anticipos e IVA siempre manuales · control interno solo revisa los lunes</t>
+  </si>
+  <si>
+    <t>Pólizas: cada contratista hace la suya — obra unifica y verifica manualmente</t>
+  </si>
+  <si>
+    <t>Sin validación automática vs. contrato · sin alerta de actualización en SINCO</t>
+  </si>
+  <si>
+    <t>OC viejas sin usar generan observaciones de auditoría · sin alerta de vencimiento</t>
+  </si>
+  <si>
+    <t>Sin alertas de recibo · sin vínculo cuenta contrato · costo indirecto sin automatizar</t>
+  </si>
+  <si>
+    <t>Contratista sin visibilidad de cortes ni pagos · FIC manual lleva mucho tiempo</t>
+  </si>
+  <si>
+    <t>Sin inducción centralizada · gestión del conocimiento ausente · ACONEX propuesto</t>
+  </si>
+  <si>
+    <t>Primeros días del mes · envío a Daiana Plata · presupuestado vs. proyectado sin automatizar</t>
+  </si>
+  <si>
+    <t>Sin dictado desde campo · sin foto adjunta · libro de obra aún en papel</t>
+  </si>
+  <si>
+    <t>Plantilla sin definir · estándar sin subir a plataforma · requiere IA</t>
+  </si>
+  <si>
+    <t>Sin responsable de bloqueo · insumos CEMEX con códigos distintos por negociación</t>
+  </si>
+  <si>
+    <t>Corte máximo día 30 · aprobación sujeta al precio del nuevo año · proceso manual</t>
+  </si>
+  <si>
+    <t>Se detectan hasta la auditoría · cierre manual · sin alerta previa</t>
+  </si>
+  <si>
+    <t>Sin foto + dictado · Calidad Cloud y BIM sin integrar · plan piloto iniciado</t>
+  </si>
+  <si>
+    <t>Sin IA que identifique antes/ahora · protocolo existe pero no se aplica</t>
+  </si>
+  <si>
+    <t>ZOHO por perfil · cuadro comparativo visible al contratista · proceso complejo</t>
+  </si>
+  <si>
+    <t>Sin visualización de volúmenes por elemento · cuadros de obra desconectados de SINCO</t>
+  </si>
+  <si>
+    <t>Múltiples firmas · seguridad social diaria manual · reporte de ingresos manual</t>
+  </si>
+  <si>
+    <t>Lecturas con criterio técnico · sin visualización automática · solo en Viale</t>
+  </si>
+  <si>
+    <t>Informes a entidades públicas manuales: acueducto, IDU, IDRD, urbanismo</t>
+  </si>
+  <si>
+    <t>Cada entidad con formato distinto · estructura mensual ya existe pero no se automatiza</t>
+  </si>
+  <si>
+    <t>Ing. Esperanza lidera estandarización · proceso en curso</t>
+  </si>
+  <si>
+    <t>Multibase con consecutivos distintos · error llega hasta contabilidad</t>
+  </si>
+  <si>
+    <t>Ya hubo pedido, OC y despacho — la aprobación del subgerente en la entrada no agrega valor · presente en VI y MA</t>
+  </si>
+  <si>
+    <t>Sin digitalización móvil · protocolos de calidad sin conexión · solo Viale</t>
+  </si>
+  <si>
+    <t>Modelo BIM no alerta sobre ejecuciones duplicadas · solo Viale</t>
+  </si>
+  <si>
+    <t>N8N y Claude para alertas · tiempos muertos · solo Reserva del Lago</t>
+  </si>
+  <si>
+    <t>Alerta de vencimiento en cortes · saldo pendiente por corte · solo Viale</t>
+  </si>
+  <si>
+    <t>Alertas de pólizas y contratos · seguimiento de amortización y retención · solo Viale</t>
+  </si>
+  <si>
+    <t>Detalle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -380,8 +586,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -400,8 +612,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0D7F5F"/>
+        <bgColor rgb="FF0D7F5F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -420,11 +638,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -435,11 +679,33 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -531,11 +797,12 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DatosExternos_1" connectionId="1" xr16:uid="{00769AA7-8B66-4DBA-AD52-A026259719B8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="13" unboundColumnsRight="2">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="14" unboundColumnsRight="2">
+    <queryTableFields count="7">
       <queryTableField id="1" name="Document ID" tableColumnId="1"/>
       <queryTableField id="2" name="contenido" tableColumnId="2"/>
       <queryTableField id="6" name="proyecto" tableColumnId="6"/>
+      <queryTableField id="13" dataBound="0" tableColumnId="5"/>
       <queryTableField id="7" name="tecnologia" tableColumnId="7"/>
       <queryTableField id="11" dataBound="0" tableColumnId="3"/>
       <queryTableField id="12" dataBound="0" tableColumnId="4"/>
@@ -553,12 +820,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DB8B03D9-BB02-4890-9DE3-8CD900B27400}" name="Notas080526_OrganizacionSubgerentes" displayName="Notas080526_OrganizacionSubgerentes" ref="A1:F33" tableType="queryTable" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="A1:F33" xr:uid="{DB8B03D9-BB02-4890-9DE3-8CD900B27400}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{CE5EA56F-CAC8-41C3-92A2-25B269DA51CE}" uniqueName="1" name="Document ID" queryTableFieldId="1" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{FDD0A4A8-FB75-41CE-A78A-7DEB9F99DA39}" uniqueName="2" name="contenido" queryTableFieldId="2" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{49A1F630-7E34-4E5F-9433-839580678B05}" uniqueName="6" name="proyecto" queryTableFieldId="6" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DB8B03D9-BB02-4890-9DE3-8CD900B27400}" name="Notas080526_OrganizacionSubgerentes" displayName="Notas080526_OrganizacionSubgerentes" ref="A1:G33" tableType="queryTable" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G33" xr:uid="{DB8B03D9-BB02-4890-9DE3-8CD900B27400}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{CE5EA56F-CAC8-41C3-92A2-25B269DA51CE}" uniqueName="1" name="Document ID" queryTableFieldId="1" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{FDD0A4A8-FB75-41CE-A78A-7DEB9F99DA39}" uniqueName="2" name="contenido" queryTableFieldId="2" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{49A1F630-7E34-4E5F-9433-839580678B05}" uniqueName="6" name="proyecto" queryTableFieldId="6" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{FF3F1D85-7CFA-4F51-99D2-85C4E91570AF}" uniqueName="5" name="Detalle" queryTableFieldId="13" dataDxfId="3">
+      <calculatedColumnFormula>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="7" xr3:uid="{C4CB7353-0F7D-425F-BDBF-998487A13EB1}" uniqueName="7" name="DOLIENTE" queryTableFieldId="7" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{542D3633-E823-4ED1-9E2E-B5F082F776E4}" uniqueName="3" name="Estado" queryTableFieldId="11" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{EC1EAE08-5EAA-4DC8-8E36-B57604BB3E29}" uniqueName="4" name="Observacion" queryTableFieldId="12" dataDxfId="0"/>
@@ -864,18 +1134,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45349E89-C281-4524-9B59-ABA483C8404D}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="74.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="65.109375" customWidth="1"/>
-    <col min="6" max="6" width="58.5546875" customWidth="1"/>
+    <col min="3" max="3" width="73.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="79.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="73.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="65.109375" customWidth="1"/>
+    <col min="7" max="7" width="58.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -886,16 +1157,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -905,13 +1179,17 @@
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Contratista sin visibilidad de cortes ni pagos · FIC manual lleva mucho tiempo</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -921,13 +1199,17 @@
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Lecturas con criterio técnico · sin visualización automática · solo en Viale</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -937,15 +1219,19 @@
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Sin visualización de volúmenes por elemento · cuadros de obra desconectados de SINCO</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -955,13 +1241,17 @@
       <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>OC viejas sin usar generan observaciones de auditoría · sin alerta de vencimiento</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -971,13 +1261,17 @@
       <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Plantilla sin definir · estándar sin subir a plataforma · requiere IA</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
@@ -987,13 +1281,17 @@
       <c r="C7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Sin dictado desde campo · sin foto adjunta · libro de obra aún en papel</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1003,15 +1301,19 @@
       <c r="C8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Sin foto + dictado · Calidad Cloud y BIM sin integrar · plan piloto iniciado</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1021,15 +1323,19 @@
       <c r="C9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Remisión del proveedor debe subirse digital a SINCO · debe traer número de OC · sin impresión de entrada</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
@@ -1039,15 +1345,19 @@
       <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>N8N y Claude para alertas · tiempos muertos · solo Reserva del Lago</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>33</v>
       </c>
@@ -1057,13 +1367,17 @@
       <c r="C11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Sin responsable de bloqueo · insumos CEMEX con códigos distintos por negociación</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -1073,15 +1387,19 @@
       <c r="C12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Multibase con consecutivos distintos · error llega hasta contabilidad</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
@@ -1091,15 +1409,19 @@
       <c r="C13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Sin digitalización móvil · protocolos de calidad sin conexión · solo Viale</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
@@ -1109,15 +1431,19 @@
       <c r="C14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Sin IA que identifique antes/ahora · protocolo existe pero no se aplica</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
@@ -1127,13 +1453,17 @@
       <c r="C15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Múltiples firmas · seguridad social diaria manual · reporte de ingresos manual</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
@@ -1143,13 +1473,17 @@
       <c r="C16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Cada obra con su cuadro · laboratorios no comparten bases · sin comparación automática con norma</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
@@ -1159,13 +1493,17 @@
       <c r="C17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Portero, ARHI, Bitácora y Temporal no articulados · proceso manual · sin bloqueo por condición médica</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>52</v>
       </c>
@@ -1175,15 +1513,19 @@
       <c r="C18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>ZOHO por perfil · cuadro comparativo visible al contratista · proceso complejo</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="2"/>
+      <c r="G18" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>54</v>
       </c>
@@ -1193,13 +1535,17 @@
       <c r="C19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Ya hubo pedido, OC y despacho — la aprobación del subgerente en la entrada no agrega valor · presente en VI y MA</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>57</v>
       </c>
@@ -1209,15 +1555,19 @@
       <c r="C20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Ing. Esperanza lidera estandarización · proceso en curso</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="2"/>
+      <c r="G20" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>60</v>
       </c>
@@ -1227,13 +1577,17 @@
       <c r="C21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Correos distintos por obra · proveedor no sabe a cuál enviar · OC no llega al proveedor</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>63</v>
       </c>
@@ -1243,13 +1597,17 @@
       <c r="C22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Sin alertas de recibo · sin vínculo cuenta contrato · costo indirecto sin automatizar</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>66</v>
       </c>
@@ -1259,13 +1617,17 @@
       <c r="C23" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Cobro tarde · equipos en desuso sin alerta · control en manos de residentes · sin preacta automática</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="2"/>
       <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>69</v>
       </c>
@@ -1275,15 +1637,19 @@
       <c r="C24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Modelo BIM no alerta sobre ejecuciones duplicadas · solo Viale</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>71</v>
       </c>
@@ -1293,15 +1659,19 @@
       <c r="C25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Corte máximo día 30 · aprobación sujeta al precio del nuevo año · proceso manual</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>73</v>
       </c>
@@ -1311,15 +1681,19 @@
       <c r="C26" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Alerta de vencimiento en cortes · saldo pendiente por corte · solo Viale</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="2"/>
+      <c r="G26" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>76</v>
       </c>
@@ -1329,13 +1703,17 @@
       <c r="C27" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Se detectan hasta la auditoría · cierre manual · sin alerta previa</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>79</v>
       </c>
@@ -1345,13 +1723,17 @@
       <c r="C28" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Sin cruce de número de contrato con pago · cuadro Excel manual · sin validación legal automatizada</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>82</v>
       </c>
@@ -1361,13 +1743,17 @@
       <c r="C29" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Pago depende de Excel · causación y pago desarticulados · tesorería sin programación automática</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>85</v>
       </c>
@@ -1377,13 +1763,17 @@
       <c r="C30" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Sin incentivos · sin conexión BIM · módulo de calidad SINCO sin explotar</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E30" s="2"/>
       <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>88</v>
       </c>
@@ -1393,13 +1783,17 @@
       <c r="C31" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Primeros días del mes · envío a Daiana Plata · presupuestado vs. proyectado sin automatizar</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E31" s="2"/>
       <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>91</v>
       </c>
@@ -1409,15 +1803,19 @@
       <c r="C32" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Alertas de pólizas y contratos · seguimiento de amortización y retención · solo Viale</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="2"/>
+      <c r="G32" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>93</v>
       </c>
@@ -1427,17 +1825,1150 @@
       <c r="C33" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="2" t="str">
+        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
+        <v>Sin inducción centralizada · gestión del conocimiento ausente · ACONEX propuesto</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E33" s="2"/>
       <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EF4E99-1C7D-4B26-A929-984CB0C54224}">
+  <dimension ref="A1:J45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="9" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6">
+        <v>4</v>
+      </c>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" s="6">
+        <v>5</v>
+      </c>
+      <c r="J3" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6">
+        <v>3</v>
+      </c>
+      <c r="J5" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6">
+        <v>3</v>
+      </c>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6">
+        <v>4</v>
+      </c>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6">
+        <v>4</v>
+      </c>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6">
+        <v>4</v>
+      </c>
+      <c r="J9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6">
+        <v>1</v>
+      </c>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6">
+        <v>4</v>
+      </c>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6">
+        <v>3</v>
+      </c>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6">
+        <v>3</v>
+      </c>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="6">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I14" s="6">
+        <v>4</v>
+      </c>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6">
+        <v>3</v>
+      </c>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6">
+        <v>1</v>
+      </c>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="6">
+        <v>3</v>
+      </c>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6">
+        <v>2</v>
+      </c>
+      <c r="J18" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="6">
+        <v>3</v>
+      </c>
+      <c r="J19" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6">
+        <v>2</v>
+      </c>
+      <c r="J20" s="6"/>
+    </row>
+    <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6">
+        <v>1</v>
+      </c>
+      <c r="J21" s="6"/>
+    </row>
+    <row r="22" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6">
+        <v>2</v>
+      </c>
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6">
+        <v>4</v>
+      </c>
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="6">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6">
+        <v>1</v>
+      </c>
+      <c r="J24" s="6"/>
+    </row>
+    <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6">
+        <v>4</v>
+      </c>
+      <c r="J25" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6">
+        <v>1</v>
+      </c>
+      <c r="J26" s="6"/>
+    </row>
+    <row r="27" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="6">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6">
+        <v>1</v>
+      </c>
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="6">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6">
+        <v>1</v>
+      </c>
+      <c r="J28" s="6"/>
+    </row>
+    <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="6">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6">
+        <v>1</v>
+      </c>
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="6">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6">
+        <v>2</v>
+      </c>
+      <c r="J30" s="6"/>
+    </row>
+    <row r="31" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="6">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6">
+        <v>1</v>
+      </c>
+      <c r="J31" s="6"/>
+    </row>
+    <row r="32" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="6">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6">
+        <v>1</v>
+      </c>
+      <c r="J32" s="6"/>
+    </row>
+    <row r="33" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="6">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6">
+        <v>1</v>
+      </c>
+      <c r="J33" s="6"/>
+    </row>
+    <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="6">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6">
+        <v>1</v>
+      </c>
+      <c r="J34" s="6"/>
+    </row>
+    <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="6">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6">
+        <v>1</v>
+      </c>
+      <c r="J35" s="6"/>
+    </row>
+    <row r="36" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="6">
+        <v>35</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6">
+        <v>1</v>
+      </c>
+      <c r="J36" s="6"/>
+    </row>
+    <row r="37" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="6">
+        <v>36</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6">
+        <v>1</v>
+      </c>
+      <c r="J37" s="6"/>
+    </row>
+    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="6">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6">
+        <v>1</v>
+      </c>
+      <c r="J38" s="6"/>
+    </row>
+    <row r="39" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="6">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6">
+        <v>1</v>
+      </c>
+      <c r="J39" s="6"/>
+    </row>
+    <row r="40" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="6">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6">
+        <v>2</v>
+      </c>
+      <c r="J40" s="6"/>
+    </row>
+    <row r="41" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="6">
+        <v>45</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6">
+        <v>1</v>
+      </c>
+      <c r="J41" s="6"/>
+    </row>
+    <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="6">
+        <v>46</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6">
+        <v>1</v>
+      </c>
+      <c r="J42" s="6"/>
+    </row>
+    <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="6">
+        <v>47</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6">
+        <v>1</v>
+      </c>
+      <c r="J43" s="6"/>
+    </row>
+    <row r="44" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="6">
+        <v>48</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6">
+        <v>1</v>
+      </c>
+      <c r="J44" s="6"/>
+    </row>
+    <row r="45" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="6">
+        <v>49</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6">
+        <v>1</v>
+      </c>
+      <c r="J45" s="6"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J45" xr:uid="{C6EF4E99-1C7D-4B26-A929-984CB0C54224}"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/Resultados080526.xlsx
+++ b/Resultados080526.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ingeurbe-my.sharepoint.com/personal/cpulgarin_construccion_com_co/Documents/1. Proyectos/1.4. Tour IA/1.4.5. Presentacion resultados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="8_{DFA57357-67B5-45DD-BE1B-46E48544B083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30BC71A0-8D68-4374-85FF-8438C8D08816}"/>
+  <xr:revisionPtr revIDLastSave="369" documentId="8_{DFA57357-67B5-45DD-BE1B-46E48544B083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59956B4B-BC4D-4B98-BDE0-398D0EC65C5A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF43666F-7D74-41D8-A8EC-929DF723E928}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="203">
   <si>
     <t>Document ID</t>
   </si>
@@ -69,9 +69,6 @@
     <t>Administrativo OTROS</t>
   </si>
   <si>
-    <t>null</t>
-  </si>
-  <si>
     <t>Portal de proveedor y portal FIC sin repositorio centralizado</t>
   </si>
   <si>
@@ -114,9 +111,6 @@
     <t>Informes mensuales: sin estándar de prompt ni plantilla automatizada</t>
   </si>
   <si>
-    <t>- Residentes Urbanismo</t>
-  </si>
-  <si>
     <t>DFKhiE3assagDgJCA7PJ</t>
   </si>
   <si>
@@ -159,9 +153,6 @@
     <t>Estandarización de insumos: inactivos sin depurar, cuentas contables incorrectas</t>
   </si>
   <si>
-    <t>- Todo</t>
-  </si>
-  <si>
     <t>LIxbzCd76LhEHTqaooBP</t>
   </si>
   <si>
@@ -339,9 +330,6 @@
     <t>Plan de calidad: formatos dispersos, sin repositorio ni estándar ATS</t>
   </si>
   <si>
-    <t>Direcotres, residentes. Debe incluirse con Leo Reyes</t>
-  </si>
-  <si>
     <t>Estado</t>
   </si>
   <si>
@@ -565,6 +553,114 @@
   </si>
   <si>
     <t>Detalle</t>
+  </si>
+  <si>
+    <t>Desarticulación entre el Portal de Proveedores y el Portal FIC por ausencia de un repositorio centralizado</t>
+  </si>
+  <si>
+    <t>Automatización del graficado de datos topográficos para el control de asentamientos</t>
+  </si>
+  <si>
+    <t>Integración de tableros BIM Power BI para el análisis de volumetría de concretos y ventanería</t>
+  </si>
+  <si>
+    <t>Gestión de órdenes de compra sin automatización de alertas de antigüedad ni cierre automático</t>
+  </si>
+  <si>
+    <t>Estandarización de prompts y automatización de plantillas para informes mensuales</t>
+  </si>
+  <si>
+    <t>Inconsistencias entre remisiones y órdenes de compra en entradas de almacén</t>
+  </si>
+  <si>
+    <t>Implementación de inteligencia artificial para la predicción de pedidos y despachos vinculados a la programación de obra</t>
+  </si>
+  <si>
+    <t>Depuración y estandarización de insumos con validación de cuentas contables</t>
+  </si>
+  <si>
+    <t>Estandarización de insumos en solicitudes de contratos entre sucursales</t>
+  </si>
+  <si>
+    <t>Registro digital de incidencias de calidad desde dispositivos móviles en campo</t>
+  </si>
+  <si>
+    <t>Optimización del proceso SSTA para permisos de inicio de semana mediante automatización</t>
+  </si>
+  <si>
+    <t>Integración y trazabilidad de horas extras con registro de causas operativas</t>
+  </si>
+  <si>
+    <t>Firma electrónica de contratos, pérdida de certificado en cada cambio</t>
+  </si>
+  <si>
+    <t>Optimización del flujo de aprobación en SGD para eliminación de validaciones redundantes posteriores a hechos cumplidos</t>
+  </si>
+  <si>
+    <t>Estandarización de formatos para soportes de cortes entre proyectos</t>
+  </si>
+  <si>
+    <t>Automatización del proceso de radicación diaria de facturas mediante bot inteligente</t>
+  </si>
+  <si>
+    <t>Implementación actas de calidad BIM - libro de obra con firma digital</t>
+  </si>
+  <si>
+    <t>Tablets para digitalización y validación electrónica de actas de calidad BIM y libro de obra</t>
+  </si>
+  <si>
+    <t>Automatización de la síntesis y trazabilidad de actas en comités de obra</t>
+  </si>
+  <si>
+    <t>Centralización y automatización del pago de servicios públicos mediante débito automático</t>
+  </si>
+  <si>
+    <t>Gestión de alquiler de equipos sin trazabilidad de inventario, hojas de vida ni mantenimiento</t>
+  </si>
+  <si>
+    <t>Detección de reprocesos por ejecución duplicada en control de cortes BIM</t>
+  </si>
+  <si>
+    <t>Integración de listas de precios e insumos en SINCO para control de precios</t>
+  </si>
+  <si>
+    <t>Automatización de alertas de vencimiento para amortizaciones y anticipos en control de cortes</t>
+  </si>
+  <si>
+    <t>Automatización de cierre y alertas de auditoría para contratos en cero</t>
+  </si>
+  <si>
+    <t>Automatización de la verificación de legalidad y pagos en procesos FIC y seguridad social</t>
+  </si>
+  <si>
+    <t>Automatización del flujo de relación de pago en SGD para eliminación de registros manuales en Excel</t>
+  </si>
+  <si>
+    <t>Integración del PAC con la programación con eliminación de registros manuales semanales</t>
+  </si>
+  <si>
+    <t>Automatización de proyecciones mensuales en el flujo SINCO–Control para directores</t>
+  </si>
+  <si>
+    <t>Automatización del control de vencimientos, amortizaciones y estados de gestión en contratos y cortes</t>
+  </si>
+  <si>
+    <t>Centralización y estandarización de formatos del plan de calidad bajo lineamientos ATS</t>
+  </si>
+  <si>
+    <t>Columna1</t>
+  </si>
+  <si>
+    <t>Bot de informe de laboratorios de concreto</t>
+  </si>
+  <si>
+    <t>Empresa</t>
+  </si>
+  <si>
+    <t>Residentes Urbanismo</t>
+  </si>
+  <si>
+    <t>Directores, residentes. Debe incluirse con Leo Reyes</t>
   </si>
 </sst>
 </file>
@@ -668,7 +764,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -691,11 +787,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -797,8 +906,8 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DatosExternos_1" connectionId="1" xr16:uid="{00769AA7-8B66-4DBA-AD52-A026259719B8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="14" unboundColumnsRight="2">
-    <queryTableFields count="7">
+  <queryTableRefresh nextId="15" unboundColumnsRight="3">
+    <queryTableFields count="8">
       <queryTableField id="1" name="Document ID" tableColumnId="1"/>
       <queryTableField id="2" name="contenido" tableColumnId="2"/>
       <queryTableField id="6" name="proyecto" tableColumnId="6"/>
@@ -806,6 +915,7 @@
       <queryTableField id="7" name="tecnologia" tableColumnId="7"/>
       <queryTableField id="11" dataBound="0" tableColumnId="3"/>
       <queryTableField id="12" dataBound="0" tableColumnId="4"/>
+      <queryTableField id="14" dataBound="0" tableColumnId="8"/>
     </queryTableFields>
     <queryTableDeletedFields count="6">
       <deletedField name="fechaCierre"/>
@@ -820,18 +930,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DB8B03D9-BB02-4890-9DE3-8CD900B27400}" name="Notas080526_OrganizacionSubgerentes" displayName="Notas080526_OrganizacionSubgerentes" ref="A1:G33" tableType="queryTable" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G33" xr:uid="{DB8B03D9-BB02-4890-9DE3-8CD900B27400}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{CE5EA56F-CAC8-41C3-92A2-25B269DA51CE}" uniqueName="1" name="Document ID" queryTableFieldId="1" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{FDD0A4A8-FB75-41CE-A78A-7DEB9F99DA39}" uniqueName="2" name="contenido" queryTableFieldId="2" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{49A1F630-7E34-4E5F-9433-839580678B05}" uniqueName="6" name="proyecto" queryTableFieldId="6" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{FF3F1D85-7CFA-4F51-99D2-85C4E91570AF}" uniqueName="5" name="Detalle" queryTableFieldId="13" dataDxfId="3">
-      <calculatedColumnFormula>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{C4CB7353-0F7D-425F-BDBF-998487A13EB1}" uniqueName="7" name="DOLIENTE" queryTableFieldId="7" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{542D3633-E823-4ED1-9E2E-B5F082F776E4}" uniqueName="3" name="Estado" queryTableFieldId="11" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{EC1EAE08-5EAA-4DC8-8E36-B57604BB3E29}" uniqueName="4" name="Observacion" queryTableFieldId="12" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DB8B03D9-BB02-4890-9DE3-8CD900B27400}" name="Notas080526_OrganizacionSubgerentes" displayName="Notas080526_OrganizacionSubgerentes" ref="A1:H33" tableType="queryTable" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H33" xr:uid="{DB8B03D9-BB02-4890-9DE3-8CD900B27400}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{CE5EA56F-CAC8-41C3-92A2-25B269DA51CE}" uniqueName="1" name="Document ID" queryTableFieldId="1" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{FDD0A4A8-FB75-41CE-A78A-7DEB9F99DA39}" uniqueName="2" name="contenido" queryTableFieldId="2" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{49A1F630-7E34-4E5F-9433-839580678B05}" uniqueName="6" name="proyecto" queryTableFieldId="6" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{FF3F1D85-7CFA-4F51-99D2-85C4E91570AF}" uniqueName="5" name="Detalle" queryTableFieldId="13" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{C4CB7353-0F7D-425F-BDBF-998487A13EB1}" uniqueName="7" name="DOLIENTE" queryTableFieldId="7" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{542D3633-E823-4ED1-9E2E-B5F082F776E4}" uniqueName="3" name="Estado" queryTableFieldId="11" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{EC1EAE08-5EAA-4DC8-8E36-B57604BB3E29}" uniqueName="4" name="Observacion" queryTableFieldId="12" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{53483D35-0AAC-44D2-8176-3548463F1BBD}" uniqueName="8" name="Columna1" queryTableFieldId="14" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1134,19 +1243,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45349E89-C281-4524-9B59-ABA483C8404D}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="74.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="124.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="79.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="73.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="99.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="65.109375" customWidth="1"/>
-    <col min="7" max="7" width="58.5546875" customWidth="1"/>
+    <col min="7" max="7" width="74.21875" customWidth="1"/>
+    <col min="8" max="8" width="103.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1157,19 +1267,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1177,663 +1290,703 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Contratista sin visibilidad de cortes ni pagos · FIC manual lleva mucho tiempo</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="C3" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Lecturas con criterio técnico · sin visualización automática · solo en Viale</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Sin visualización de volúmenes por elemento · cuadros de obra desconectados de SINCO</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="C5" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D5" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>OC viejas sin usar generan observaciones de auditoría · sin alerta de vencimiento</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Plantilla sin definir · estándar sin subir a plataforma · requiere IA</v>
+        <v>171</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Sin dictado desde campo · sin foto adjunta · libro de obra aún en papel</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Sin foto + dictado · Calidad Cloud y BIM sin integrar · plan piloto iniciado</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Remisión del proveedor debe subirse digital a SINCO · debe traer número de OC · sin impresión de entrada</v>
+        <v>172</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>N8N y Claude para alertas · tiempos muertos · solo Reserva del Lago</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Sin responsable de bloqueo · insumos CEMEX con códigos distintos por negociación</v>
+        <v>174</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Multibase con consecutivos distintos · error llega hasta contabilidad</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="2" t="s">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Sin digitalización móvil · protocolos de calidad sin conexión · solo Viale</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Sin IA que identifique antes/ahora · protocolo existe pero no se aplica</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Múltiples firmas · seguridad social diaria manual · reporte de ingresos manual</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Cada obra con su cuadro · laboratorios no comparten bases · sin comparación automática con norma</v>
+        <v>199</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Portero, ARHI, Bitácora y Temporal no articulados · proceso manual · sin bloqueo por condición médica</v>
+        <v>178</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>ZOHO por perfil · cuadro comparativo visible al contratista · proceso complejo</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Ya hubo pedido, OC y despacho — la aprobación del subgerente en la entrada no agrega valor · presente en VI y MA</v>
+        <v>180</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Ing. Esperanza lidera estandarización · proceso en curso</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Correos distintos por obra · proveedor no sabe a cuál enviar · OC no llega al proveedor</v>
+        <v>182</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Sin alertas de recibo · sin vínculo cuenta contrato · costo indirecto sin automatizar</v>
+        <v>186</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Cobro tarde · equipos en desuso sin alerta · control en manos de residentes · sin preacta automática</v>
+        <v>187</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="2" t="s">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Modelo BIM no alerta sobre ejecuciones duplicadas · solo Viale</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Corte máximo día 30 · aprobación sujeta al precio del nuevo año · proceso manual</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="B26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Alerta de vencimiento en cortes · saldo pendiente por corte · solo Viale</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Se detectan hasta la auditoría · cierre manual · sin alerta previa</v>
+        <v>191</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D28" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Sin cruce de número de contrato con pago · cuadro Excel manual · sin validación legal automatizada</v>
+        <v>192</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Pago depende de Excel · causación y pago desarticulados · tesorería sin programación automática</v>
+        <v>193</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D30" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Sin incentivos · sin conexión BIM · módulo de calidad SINCO sin explotar</v>
+        <v>194</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Primeros días del mes · envío a Daiana Plata · presupuestado vs. proyectado sin automatizar</v>
+        <v>195</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Alertas de pólizas y contratos · seguimiento de amortización y retención · solo Viale</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" s="2" t="str">
-        <f>+VLOOKUP(Notas080526_OrganizacionSubgerentes[[#This Row],[proyecto]],'Por Frecuencia'!$B$2:$C$45,2,FALSE)</f>
-        <v>Sin inducción centralizada · gestión del conocimiento ausente · ACONEX propuesto</v>
+        <v>197</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>95</v>
+        <v>202</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
+      <c r="H33" s="8" t="s">
+        <v>91</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1856,34 +2009,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -1891,22 +2044,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6">
@@ -1919,25 +2072,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I3" s="6">
         <v>5</v>
@@ -1951,22 +2104,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6">
@@ -1979,19 +2132,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -2007,19 +2160,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
@@ -2033,22 +2186,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6">
@@ -2061,22 +2214,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6">
@@ -2089,22 +2242,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6">
@@ -2119,16 +2272,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6">
@@ -2141,22 +2294,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6">
@@ -2169,19 +2322,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -2195,19 +2348,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -2221,23 +2374,23 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I14" s="6">
         <v>4</v>
@@ -2249,20 +2402,20 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6">
@@ -2275,16 +2428,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6">
@@ -2297,21 +2450,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I17" s="6">
         <v>3</v>
@@ -2323,17 +2476,17 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -2349,21 +2502,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I19" s="6">
         <v>3</v>
@@ -2377,18 +2530,18 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="6">
@@ -2401,16 +2554,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6">
@@ -2423,18 +2576,18 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6">
@@ -2447,22 +2600,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6">
@@ -2475,15 +2628,15 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
       <c r="F24" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -2497,22 +2650,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="6">
@@ -2527,16 +2680,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="6">
@@ -2549,16 +2702,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6">
@@ -2571,16 +2724,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="6">
@@ -2593,16 +2746,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6">
@@ -2615,18 +2768,18 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="6">
@@ -2639,16 +2792,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6">
@@ -2661,15 +2814,15 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
@@ -2683,15 +2836,15 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
@@ -2705,15 +2858,15 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -2727,15 +2880,15 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -2749,14 +2902,14 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
@@ -2771,15 +2924,15 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
       <c r="F37" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -2793,16 +2946,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6">
@@ -2815,16 +2968,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6">
@@ -2837,17 +2990,17 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
@@ -2861,14 +3014,14 @@
         <v>45</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
@@ -2883,14 +3036,14 @@
         <v>46</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
@@ -2905,13 +3058,13 @@
         <v>47</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
@@ -2927,14 +3080,14 @@
         <v>48</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
@@ -2949,14 +3102,14 @@
         <v>49</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
